--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2742,9 +2742,9 @@
           <t>Albuquerque, NM; Hardcopy</t>
         </is>
       </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>Plymouth; Hardcopy</t>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>Plymouth; Digital</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr"/>
@@ -2974,9 +2974,9 @@
           <t>?; Pending (Brit)</t>
         </is>
       </c>
-      <c r="F108" s="18" t="inlineStr">
-        <is>
-          <t>Valencia; Digital</t>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>Valencia; Ingested</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35">
@@ -3968,7 +3968,7 @@
         <v>99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1428</v>
+        <v>1517</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2794,9 +2794,9 @@
           <t>Reno, NV (123); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="13" t="inlineStr">
-        <is>
-          <t>Peniche; Hardcopy</t>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>Peniche; Digital</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr"/>
@@ -2842,9 +2842,9 @@
           <t>Austin, TX; Hardcopy</t>
         </is>
       </c>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>Amsterdam; Hardcopy</t>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>Amsterdam; Digital</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr"/>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2832,14 +2832,14 @@
       <c r="A103" s="10" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="13" t="inlineStr">
-        <is>
-          <t>Austin, TX; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C103" s="13" t="inlineStr">
-        <is>
-          <t>Austin, TX; Hardcopy</t>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>Austin, TX; Digital</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>Austin, TX; Digital</t>
         </is>
       </c>
       <c r="D103" s="18" t="inlineStr">
@@ -2884,14 +2884,14 @@
       <c r="A105" s="10" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Hardcopy</t>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Digital</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Digital</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -42,7 +42,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F6B26B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9CB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,7 +131,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,16 +145,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -936,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -968,7 +977,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No known source</t>
+          <t>No known source anywhere</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -989,12 +998,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digital PDF exists but not yet ingested</t>
+          <t>Digital PROGRAMME/schedule held, but NOT full abstracts — the abstract book is still needed (see note)</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -1002,12 +1011,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OCR'd &amp; ingested but low-confidence (needs_review) — old degraded scans</t>
+          <t>Digital ABSTRACT BOOK held &amp; ingestable, not yet ingested</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1015,12 +1024,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Program book ingested: titles/authors/type, NO abstract bodies</t>
+          <t>Full abstracts ingested but from degraded scans (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -1028,12 +1037,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ingested</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Full abstracts ingested into the DB</t>
+          <t>Programme ingested: titles/authors/type, NO abstract bodies</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -1041,84 +1050,97 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Ingested</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Full abstracts ingested into the DB</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Being collated by an external contact (OCS: Brit Finucci)</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Available from an external contact, not yet obtained (EEA: Cat; OCS: Brit)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NOTES:</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
+          <t>NOTES:</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
+          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
+          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans will upgrade these.</t>
+          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- No abstracts collected pre-1992 (Carylanne's archive starts 1992) → 1916-1991 show host city but 'Missing'.</t>
+          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans will upgrade these.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA not yet ingested. SI2022 Valencia PDF received (Digital).</t>
+          <t>- No abstracts collected pre-1992 (Carylanne's archive starts 1992) → 1916-1991 show host city but 'Missing'.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
+          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA not yet ingested. SI2022 Valencia PDF received (Digital).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>- Per-society counts &amp; trends: see the Dashboard tab.</t>
         </is>
@@ -1139,1942 +1161,1942 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>ASIH/JMIH</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>AES</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>EEA</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>OCS</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="11" t="n">
         <v>1916</v>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr"/>
-      <c r="D2" s="12" t="inlineStr"/>
-      <c r="E2" s="12" t="inlineStr"/>
-      <c r="F2" s="12" t="inlineStr"/>
+      <c r="C2" s="13" t="inlineStr"/>
+      <c r="D2" s="13" t="inlineStr"/>
+      <c r="E2" s="13" t="inlineStr"/>
+      <c r="F2" s="13" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="11" t="n">
         <v>1917</v>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr"/>
-      <c r="D3" s="12" t="inlineStr"/>
-      <c r="E3" s="12" t="inlineStr"/>
-      <c r="F3" s="12" t="inlineStr"/>
+      <c r="C3" s="13" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr"/>
+      <c r="E3" s="13" t="inlineStr"/>
+      <c r="F3" s="13" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="11" t="n">
         <v>1918</v>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Brooklyn, NY; Missing</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="12" t="inlineStr"/>
-      <c r="E4" s="12" t="inlineStr"/>
-      <c r="F4" s="12" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr"/>
+      <c r="D4" s="13" t="inlineStr"/>
+      <c r="E4" s="13" t="inlineStr"/>
+      <c r="F4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="11" t="n">
         <v>1919</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="12" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="12" t="inlineStr"/>
+      <c r="C5" s="13" t="inlineStr"/>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="11" t="n">
         <v>1920</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="12" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="11" t="n">
         <v>1921</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="12" t="inlineStr"/>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="11" t="n">
         <v>1922</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="12" t="inlineStr"/>
+      <c r="C8" s="13" t="inlineStr"/>
+      <c r="D8" s="13" t="inlineStr"/>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="11" t="n">
         <v>1923</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="11" t="n">
         <v>1924</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Northhampton, MA; Missing</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="12" t="inlineStr"/>
-      <c r="F10" s="12" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr"/>
+      <c r="F10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="11" t="n">
         <v>1925</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
-      <c r="F11" s="12" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="11" t="n">
         <v>1926</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr"/>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="12" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="11" t="n">
         <v>1927</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr"/>
-      <c r="E13" s="12" t="inlineStr"/>
-      <c r="F13" s="12" t="inlineStr"/>
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr"/>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="11" t="n">
         <v>1928</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr"/>
-      <c r="D14" s="12" t="inlineStr"/>
-      <c r="E14" s="12" t="inlineStr"/>
-      <c r="F14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr"/>
+      <c r="E14" s="13" t="inlineStr"/>
+      <c r="F14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="11" t="n">
         <v>1929</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="12" t="inlineStr"/>
-      <c r="F15" s="12" t="inlineStr"/>
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr"/>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="11" t="n">
         <v>1930</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr"/>
-      <c r="D16" s="12" t="inlineStr"/>
-      <c r="E16" s="12" t="inlineStr"/>
-      <c r="F16" s="12" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="11" t="n">
         <v>1931</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>Philadelphia, PA; Missing</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr"/>
-      <c r="E17" s="12" t="inlineStr"/>
-      <c r="F17" s="12" t="inlineStr"/>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr"/>
+      <c r="E17" s="13" t="inlineStr"/>
+      <c r="F17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="11" t="n">
         <v>1932</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr"/>
-      <c r="E18" s="12" t="inlineStr"/>
-      <c r="F18" s="12" t="inlineStr"/>
+      <c r="C18" s="13" t="inlineStr"/>
+      <c r="D18" s="13" t="inlineStr"/>
+      <c r="E18" s="13" t="inlineStr"/>
+      <c r="F18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="11" t="n">
         <v>1933</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>Cambridge, MA; Missing</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12" t="inlineStr"/>
-      <c r="F19" s="12" t="inlineStr"/>
+      <c r="C19" s="13" t="inlineStr"/>
+      <c r="D19" s="13" t="inlineStr"/>
+      <c r="E19" s="13" t="inlineStr"/>
+      <c r="F19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="11" t="n">
         <v>1934</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="12" t="inlineStr"/>
-      <c r="E20" s="12" t="inlineStr"/>
-      <c r="F20" s="12" t="inlineStr"/>
+      <c r="C20" s="13" t="inlineStr"/>
+      <c r="D20" s="13" t="inlineStr"/>
+      <c r="E20" s="13" t="inlineStr"/>
+      <c r="F20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="11" t="n">
         <v>1935</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
-      <c r="D21" s="12" t="inlineStr"/>
-      <c r="E21" s="12" t="inlineStr"/>
-      <c r="F21" s="12" t="inlineStr"/>
+      <c r="C21" s="13" t="inlineStr"/>
+      <c r="D21" s="13" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="11" t="n">
         <v>1936</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr"/>
-      <c r="E22" s="12" t="inlineStr"/>
-      <c r="F22" s="12" t="inlineStr"/>
+      <c r="C22" s="13" t="inlineStr"/>
+      <c r="D22" s="13" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="11" t="n">
         <v>1937</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
-      <c r="D23" s="12" t="inlineStr"/>
-      <c r="E23" s="12" t="inlineStr"/>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="C23" s="13" t="inlineStr"/>
+      <c r="D23" s="13" t="inlineStr"/>
+      <c r="E23" s="13" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="11" t="n">
         <v>1938</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Berkeley, CA; Missing</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr"/>
-      <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="12" t="inlineStr"/>
-      <c r="F24" s="12" t="inlineStr"/>
+      <c r="C24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr"/>
+      <c r="E24" s="13" t="inlineStr"/>
+      <c r="F24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="11" t="n">
         <v>1939</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr"/>
-      <c r="D25" s="12" t="inlineStr"/>
-      <c r="E25" s="12" t="inlineStr"/>
-      <c r="F25" s="12" t="inlineStr"/>
+      <c r="C25" s="13" t="inlineStr"/>
+      <c r="D25" s="13" t="inlineStr"/>
+      <c r="E25" s="13" t="inlineStr"/>
+      <c r="F25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="11" t="n">
         <v>1940</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>Toronto, ON; Missing</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr"/>
-      <c r="E26" s="12" t="inlineStr"/>
-      <c r="F26" s="12" t="inlineStr"/>
+      <c r="C26" s="13" t="inlineStr"/>
+      <c r="D26" s="13" t="inlineStr"/>
+      <c r="E26" s="13" t="inlineStr"/>
+      <c r="F26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="11" t="n">
         <v>1941</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
-      <c r="D27" s="12" t="inlineStr"/>
-      <c r="E27" s="12" t="inlineStr"/>
-      <c r="F27" s="12" t="inlineStr"/>
+      <c r="C27" s="13" t="inlineStr"/>
+      <c r="D27" s="13" t="inlineStr"/>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>1942</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr"/>
-      <c r="D28" s="12" t="inlineStr"/>
-      <c r="E28" s="12" t="inlineStr"/>
-      <c r="F28" s="12" t="inlineStr"/>
+      <c r="C28" s="13" t="inlineStr"/>
+      <c r="D28" s="13" t="inlineStr"/>
+      <c r="E28" s="13" t="inlineStr"/>
+      <c r="F28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="11" t="n">
         <v>1943</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr"/>
-      <c r="D29" s="12" t="inlineStr"/>
-      <c r="E29" s="12" t="inlineStr"/>
-      <c r="F29" s="12" t="inlineStr"/>
+      <c r="C29" s="13" t="inlineStr"/>
+      <c r="D29" s="13" t="inlineStr"/>
+      <c r="E29" s="13" t="inlineStr"/>
+      <c r="F29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="11" t="n">
         <v>1944</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr"/>
-      <c r="D30" s="12" t="inlineStr"/>
-      <c r="E30" s="12" t="inlineStr"/>
-      <c r="F30" s="12" t="inlineStr"/>
+      <c r="C30" s="13" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr"/>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="11" t="n">
         <v>1945</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>?; Missing</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="12" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
+      <c r="C31" s="13" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr"/>
+      <c r="E31" s="13" t="inlineStr"/>
+      <c r="F31" s="13" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="11" t="n">
         <v>1946</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Missing</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr"/>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="12" t="inlineStr"/>
-      <c r="F32" s="12" t="inlineStr"/>
+      <c r="C32" s="13" t="inlineStr"/>
+      <c r="D32" s="13" t="inlineStr"/>
+      <c r="E32" s="13" t="inlineStr"/>
+      <c r="F32" s="13" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="11" t="n">
         <v>1947</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="12" t="inlineStr"/>
-      <c r="F33" s="12" t="inlineStr"/>
+      <c r="C33" s="13" t="inlineStr"/>
+      <c r="D33" s="13" t="inlineStr"/>
+      <c r="E33" s="13" t="inlineStr"/>
+      <c r="F33" s="13" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="11" t="n">
         <v>1948</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr"/>
-      <c r="D34" s="12" t="inlineStr"/>
-      <c r="E34" s="12" t="inlineStr"/>
-      <c r="F34" s="12" t="inlineStr"/>
+      <c r="C34" s="13" t="inlineStr"/>
+      <c r="D34" s="13" t="inlineStr"/>
+      <c r="E34" s="13" t="inlineStr"/>
+      <c r="F34" s="13" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="11" t="n">
         <v>1949</v>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr"/>
-      <c r="D35" s="12" t="inlineStr"/>
-      <c r="E35" s="12" t="inlineStr"/>
-      <c r="F35" s="12" t="inlineStr"/>
+      <c r="C35" s="13" t="inlineStr"/>
+      <c r="D35" s="13" t="inlineStr"/>
+      <c r="E35" s="13" t="inlineStr"/>
+      <c r="F35" s="13" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="11" t="n">
         <v>1950</v>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Salt Lake City, UT; Missing</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr"/>
-      <c r="D36" s="12" t="inlineStr"/>
-      <c r="E36" s="12" t="inlineStr"/>
-      <c r="F36" s="12" t="inlineStr"/>
+      <c r="C36" s="13" t="inlineStr"/>
+      <c r="D36" s="13" t="inlineStr"/>
+      <c r="E36" s="13" t="inlineStr"/>
+      <c r="F36" s="13" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="11" t="n">
         <v>1951</v>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr"/>
-      <c r="D37" s="12" t="inlineStr"/>
-      <c r="E37" s="12" t="inlineStr"/>
-      <c r="F37" s="12" t="inlineStr"/>
+      <c r="C37" s="13" t="inlineStr"/>
+      <c r="D37" s="13" t="inlineStr"/>
+      <c r="E37" s="13" t="inlineStr"/>
+      <c r="F37" s="13" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="11" t="n">
         <v>1952</v>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr"/>
-      <c r="D38" s="12" t="inlineStr"/>
-      <c r="E38" s="12" t="inlineStr"/>
-      <c r="F38" s="12" t="inlineStr"/>
+      <c r="C38" s="13" t="inlineStr"/>
+      <c r="D38" s="13" t="inlineStr"/>
+      <c r="E38" s="13" t="inlineStr"/>
+      <c r="F38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="11" t="n">
         <v>1953</v>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr"/>
-      <c r="D39" s="12" t="inlineStr"/>
-      <c r="E39" s="12" t="inlineStr"/>
-      <c r="F39" s="12" t="inlineStr"/>
+      <c r="C39" s="13" t="inlineStr"/>
+      <c r="D39" s="13" t="inlineStr"/>
+      <c r="E39" s="13" t="inlineStr"/>
+      <c r="F39" s="13" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="11" t="n">
         <v>1954</v>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr"/>
-      <c r="D40" s="12" t="inlineStr"/>
-      <c r="E40" s="12" t="inlineStr"/>
-      <c r="F40" s="12" t="inlineStr"/>
+      <c r="C40" s="13" t="inlineStr"/>
+      <c r="D40" s="13" t="inlineStr"/>
+      <c r="E40" s="13" t="inlineStr"/>
+      <c r="F40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="11" t="n">
         <v>1955</v>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr"/>
-      <c r="D41" s="12" t="inlineStr"/>
-      <c r="E41" s="12" t="inlineStr"/>
-      <c r="F41" s="12" t="inlineStr"/>
+      <c r="C41" s="13" t="inlineStr"/>
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="13" t="inlineStr"/>
+      <c r="F41" s="13" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="11" t="n">
         <v>1956</v>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Higgins Lake, MI; Missing</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr"/>
-      <c r="D42" s="12" t="inlineStr"/>
-      <c r="E42" s="12" t="inlineStr"/>
-      <c r="F42" s="12" t="inlineStr"/>
+      <c r="C42" s="13" t="inlineStr"/>
+      <c r="D42" s="13" t="inlineStr"/>
+      <c r="E42" s="13" t="inlineStr"/>
+      <c r="F42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="11" t="n">
         <v>1957</v>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr"/>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
-      <c r="F43" s="12" t="inlineStr"/>
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="13" t="inlineStr"/>
+      <c r="F43" s="13" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="11" t="n">
         <v>1958</v>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>Bloomington, IN; Missing</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr"/>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="C44" s="13" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="13" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="11" t="n">
         <v>1959</v>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>San Diego, CA; Missing</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr"/>
-      <c r="D45" s="12" t="inlineStr"/>
-      <c r="E45" s="12" t="inlineStr"/>
-      <c r="F45" s="12" t="inlineStr"/>
+      <c r="C45" s="13" t="inlineStr"/>
+      <c r="D45" s="13" t="inlineStr"/>
+      <c r="E45" s="13" t="inlineStr"/>
+      <c r="F45" s="13" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="11" t="n">
         <v>1960</v>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>Chicago, IL; Missing</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr"/>
-      <c r="D46" s="12" t="inlineStr"/>
-      <c r="E46" s="12" t="inlineStr"/>
-      <c r="F46" s="12" t="inlineStr"/>
+      <c r="C46" s="13" t="inlineStr"/>
+      <c r="D46" s="13" t="inlineStr"/>
+      <c r="E46" s="13" t="inlineStr"/>
+      <c r="F46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="11" t="n">
         <v>1961</v>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Austin, TX; Missing</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr"/>
-      <c r="D47" s="12" t="inlineStr"/>
-      <c r="E47" s="12" t="inlineStr"/>
-      <c r="F47" s="12" t="inlineStr"/>
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="13" t="inlineStr"/>
+      <c r="F47" s="13" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n">
+      <c r="A48" s="11" t="n">
         <v>1962</v>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>Washington, DC; Missing</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr"/>
-      <c r="D48" s="12" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr"/>
-      <c r="F48" s="12" t="inlineStr"/>
+      <c r="C48" s="13" t="inlineStr"/>
+      <c r="D48" s="13" t="inlineStr"/>
+      <c r="E48" s="13" t="inlineStr"/>
+      <c r="F48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="11" t="n">
         <v>1963</v>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Vancouver, BC; Missing</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr"/>
-      <c r="D49" s="12" t="inlineStr"/>
-      <c r="E49" s="12" t="inlineStr"/>
-      <c r="F49" s="12" t="inlineStr"/>
+      <c r="C49" s="13" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr"/>
+      <c r="E49" s="13" t="inlineStr"/>
+      <c r="F49" s="13" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n">
+      <c r="A50" s="11" t="n">
         <v>1964</v>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Morehead City, NC; Missing</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr"/>
-      <c r="D50" s="12" t="inlineStr"/>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr"/>
+      <c r="C50" s="13" t="inlineStr"/>
+      <c r="D50" s="13" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr"/>
+      <c r="F50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" s="11" t="n">
         <v>1965</v>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>Lawrence, KS; Missing</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr"/>
-      <c r="D51" s="12" t="inlineStr"/>
-      <c r="E51" s="12" t="inlineStr"/>
-      <c r="F51" s="12" t="inlineStr"/>
+      <c r="C51" s="13" t="inlineStr"/>
+      <c r="D51" s="13" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr"/>
+      <c r="F51" s="13" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="10" t="n">
+      <c r="A52" s="11" t="n">
         <v>1966</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>Miami, FL; Missing</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr"/>
-      <c r="D52" s="12" t="inlineStr"/>
-      <c r="E52" s="12" t="inlineStr"/>
-      <c r="F52" s="12" t="inlineStr"/>
+      <c r="C52" s="13" t="inlineStr"/>
+      <c r="D52" s="13" t="inlineStr"/>
+      <c r="E52" s="13" t="inlineStr"/>
+      <c r="F52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="10" t="n">
+      <c r="A53" s="11" t="n">
         <v>1967</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr"/>
-      <c r="D53" s="12" t="inlineStr"/>
-      <c r="E53" s="12" t="inlineStr"/>
-      <c r="F53" s="12" t="inlineStr"/>
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="13" t="inlineStr"/>
+      <c r="F53" s="13" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="11" t="n">
         <v>1968</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr"/>
-      <c r="D54" s="12" t="inlineStr"/>
-      <c r="E54" s="12" t="inlineStr"/>
-      <c r="F54" s="12" t="inlineStr"/>
+      <c r="C54" s="13" t="inlineStr"/>
+      <c r="D54" s="13" t="inlineStr"/>
+      <c r="E54" s="13" t="inlineStr"/>
+      <c r="F54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="11" t="n">
         <v>1969</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr"/>
-      <c r="D55" s="12" t="inlineStr"/>
-      <c r="E55" s="12" t="inlineStr"/>
-      <c r="F55" s="12" t="inlineStr"/>
+      <c r="C55" s="13" t="inlineStr"/>
+      <c r="D55" s="13" t="inlineStr"/>
+      <c r="E55" s="13" t="inlineStr"/>
+      <c r="F55" s="13" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="n">
+      <c r="A56" s="11" t="n">
         <v>1970</v>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>New Orleans, LA; Missing</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr"/>
-      <c r="D56" s="12" t="inlineStr"/>
-      <c r="E56" s="12" t="inlineStr"/>
-      <c r="F56" s="12" t="inlineStr"/>
+      <c r="C56" s="13" t="inlineStr"/>
+      <c r="D56" s="13" t="inlineStr"/>
+      <c r="E56" s="13" t="inlineStr"/>
+      <c r="F56" s="13" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="A57" s="11" t="n">
         <v>1971</v>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Missing</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr"/>
-      <c r="D57" s="12" t="inlineStr"/>
-      <c r="E57" s="12" t="inlineStr"/>
-      <c r="F57" s="12" t="inlineStr"/>
+      <c r="C57" s="13" t="inlineStr"/>
+      <c r="D57" s="13" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr"/>
+      <c r="F57" s="13" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="11" t="n">
         <v>1972</v>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Boston, MA; Missing</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr"/>
-      <c r="D58" s="12" t="inlineStr"/>
-      <c r="E58" s="12" t="inlineStr"/>
-      <c r="F58" s="12" t="inlineStr"/>
+      <c r="C58" s="13" t="inlineStr"/>
+      <c r="D58" s="13" t="inlineStr"/>
+      <c r="E58" s="13" t="inlineStr"/>
+      <c r="F58" s="13" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="A59" s="11" t="n">
         <v>1973</v>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>San Jose, Costa Rica; Missing</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr"/>
-      <c r="D59" s="12" t="inlineStr"/>
-      <c r="E59" s="12" t="inlineStr"/>
-      <c r="F59" s="12" t="inlineStr"/>
+      <c r="C59" s="13" t="inlineStr"/>
+      <c r="D59" s="13" t="inlineStr"/>
+      <c r="E59" s="13" t="inlineStr"/>
+      <c r="F59" s="13" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="11" t="n">
         <v>1974</v>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>Ottawa, ON; Missing</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr"/>
-      <c r="D60" s="12" t="inlineStr"/>
-      <c r="E60" s="12" t="inlineStr"/>
-      <c r="F60" s="12" t="inlineStr"/>
+      <c r="C60" s="13" t="inlineStr"/>
+      <c r="D60" s="13" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr"/>
+      <c r="F60" s="13" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" s="11" t="n">
         <v>1975</v>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>Williamsburg, VA; Missing</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr"/>
-      <c r="D61" s="12" t="inlineStr"/>
-      <c r="E61" s="12" t="inlineStr"/>
-      <c r="F61" s="12" t="inlineStr"/>
+      <c r="C61" s="13" t="inlineStr"/>
+      <c r="D61" s="13" t="inlineStr"/>
+      <c r="E61" s="13" t="inlineStr"/>
+      <c r="F61" s="13" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="11" t="n">
         <v>1976</v>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>Fairbanks, AK; Missing</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr"/>
-      <c r="D62" s="12" t="inlineStr"/>
-      <c r="E62" s="12" t="inlineStr"/>
-      <c r="F62" s="12" t="inlineStr"/>
+      <c r="C62" s="13" t="inlineStr"/>
+      <c r="D62" s="13" t="inlineStr"/>
+      <c r="E62" s="13" t="inlineStr"/>
+      <c r="F62" s="13" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" s="11" t="n">
         <v>1977</v>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>Gainesville, FL; Missing</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr"/>
-      <c r="D63" s="12" t="inlineStr"/>
-      <c r="E63" s="12" t="inlineStr"/>
-      <c r="F63" s="12" t="inlineStr"/>
+      <c r="C63" s="13" t="inlineStr"/>
+      <c r="D63" s="13" t="inlineStr"/>
+      <c r="E63" s="13" t="inlineStr"/>
+      <c r="F63" s="13" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n">
+      <c r="A64" s="11" t="n">
         <v>1978</v>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>Tempe, AZ; Missing</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr"/>
-      <c r="D64" s="12" t="inlineStr"/>
-      <c r="E64" s="12" t="inlineStr"/>
-      <c r="F64" s="12" t="inlineStr"/>
+      <c r="C64" s="13" t="inlineStr"/>
+      <c r="D64" s="13" t="inlineStr"/>
+      <c r="E64" s="13" t="inlineStr"/>
+      <c r="F64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="n">
+      <c r="A65" s="11" t="n">
         <v>1979</v>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>Orono, ME; Missing</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr"/>
-      <c r="D65" s="12" t="inlineStr"/>
-      <c r="E65" s="12" t="inlineStr"/>
-      <c r="F65" s="12" t="inlineStr"/>
+      <c r="C65" s="13" t="inlineStr"/>
+      <c r="D65" s="13" t="inlineStr"/>
+      <c r="E65" s="13" t="inlineStr"/>
+      <c r="F65" s="13" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="11" t="n">
         <v>1980</v>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>Fort Worth, TX; Missing</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr"/>
-      <c r="D66" s="12" t="inlineStr"/>
-      <c r="E66" s="12" t="inlineStr"/>
-      <c r="F66" s="12" t="inlineStr"/>
+      <c r="C66" s="13" t="inlineStr"/>
+      <c r="D66" s="13" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr"/>
+      <c r="F66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="10" t="n">
+      <c r="A67" s="11" t="n">
         <v>1981</v>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>Corvallis, OR; Missing</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr"/>
-      <c r="D67" s="12" t="inlineStr"/>
-      <c r="E67" s="12" t="inlineStr"/>
-      <c r="F67" s="12" t="inlineStr"/>
+      <c r="C67" s="13" t="inlineStr"/>
+      <c r="D67" s="13" t="inlineStr"/>
+      <c r="E67" s="13" t="inlineStr"/>
+      <c r="F67" s="13" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="n">
+      <c r="A68" s="11" t="n">
         <v>1982</v>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>DeKalb, IL; Missing</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr"/>
-      <c r="D68" s="12" t="inlineStr"/>
-      <c r="E68" s="12" t="inlineStr"/>
-      <c r="F68" s="12" t="inlineStr"/>
+      <c r="C68" s="13" t="inlineStr"/>
+      <c r="D68" s="13" t="inlineStr"/>
+      <c r="E68" s="13" t="inlineStr"/>
+      <c r="F68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="n">
+      <c r="A69" s="11" t="n">
         <v>1983</v>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>Tallahasee, FL; Missing</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr"/>
-      <c r="E69" s="12" t="inlineStr"/>
-      <c r="F69" s="12" t="inlineStr"/>
+      <c r="D69" s="13" t="inlineStr"/>
+      <c r="E69" s="13" t="inlineStr"/>
+      <c r="F69" s="13" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="n">
+      <c r="A70" s="11" t="n">
         <v>1984</v>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="C70" s="11" t="inlineStr">
+      <c r="C70" s="12" t="inlineStr">
         <is>
           <t>Norman, OK; Missing</t>
         </is>
       </c>
-      <c r="D70" s="12" t="inlineStr"/>
-      <c r="E70" s="12" t="inlineStr"/>
-      <c r="F70" s="12" t="inlineStr"/>
+      <c r="D70" s="13" t="inlineStr"/>
+      <c r="E70" s="13" t="inlineStr"/>
+      <c r="F70" s="13" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="n">
+      <c r="A71" s="11" t="n">
         <v>1985</v>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="C71" s="11" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr"/>
-      <c r="E71" s="12" t="inlineStr"/>
-      <c r="F71" s="12" t="inlineStr"/>
+      <c r="D71" s="13" t="inlineStr"/>
+      <c r="E71" s="13" t="inlineStr"/>
+      <c r="F71" s="13" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="10" t="n">
+      <c r="A72" s="11" t="n">
         <v>1986</v>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="C72" s="11" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr"/>
-      <c r="E72" s="12" t="inlineStr"/>
-      <c r="F72" s="12" t="inlineStr"/>
+      <c r="D72" s="13" t="inlineStr"/>
+      <c r="E72" s="13" t="inlineStr"/>
+      <c r="F72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="10" t="n">
+      <c r="A73" s="11" t="n">
         <v>1987</v>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="C73" s="11" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr"/>
-      <c r="E73" s="12" t="inlineStr"/>
-      <c r="F73" s="12" t="inlineStr"/>
+      <c r="D73" s="13" t="inlineStr"/>
+      <c r="E73" s="13" t="inlineStr"/>
+      <c r="F73" s="13" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="n">
+      <c r="A74" s="11" t="n">
         <v>1988</v>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C74" s="11" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr"/>
-      <c r="E74" s="12" t="inlineStr"/>
-      <c r="F74" s="12" t="inlineStr"/>
+      <c r="D74" s="13" t="inlineStr"/>
+      <c r="E74" s="13" t="inlineStr"/>
+      <c r="F74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="n">
+      <c r="A75" s="11" t="n">
         <v>1989</v>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr"/>
-      <c r="E75" s="12" t="inlineStr"/>
-      <c r="F75" s="12" t="inlineStr"/>
+      <c r="D75" s="13" t="inlineStr"/>
+      <c r="E75" s="13" t="inlineStr"/>
+      <c r="F75" s="13" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n">
+      <c r="A76" s="11" t="n">
         <v>1990</v>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr"/>
-      <c r="E76" s="12" t="inlineStr"/>
-      <c r="F76" s="12" t="inlineStr"/>
+      <c r="D76" s="13" t="inlineStr"/>
+      <c r="E76" s="13" t="inlineStr"/>
+      <c r="F76" s="13" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" s="11" t="n">
         <v>1991</v>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C77" s="11" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="D77" s="12" t="inlineStr"/>
-      <c r="E77" s="12" t="inlineStr"/>
-      <c r="F77" s="12" t="inlineStr"/>
+      <c r="D77" s="13" t="inlineStr"/>
+      <c r="E77" s="13" t="inlineStr"/>
+      <c r="F77" s="13" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="n">
+      <c r="A78" s="11" t="n">
         <v>1992</v>
       </c>
-      <c r="B78" s="13" t="inlineStr">
-        <is>
-          <t>Champaign-Urbana, IL; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>Champaign-Urbana, IL; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr"/>
-      <c r="E78" s="12" t="inlineStr"/>
-      <c r="F78" s="12" t="inlineStr"/>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr"/>
+      <c r="E78" s="13" t="inlineStr"/>
+      <c r="F78" s="13" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n">
+      <c r="A79" s="11" t="n">
         <v>1993</v>
       </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Austin, TX; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>Austin, TX; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr"/>
-      <c r="E79" s="12" t="inlineStr"/>
-      <c r="F79" s="12" t="inlineStr"/>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr"/>
+      <c r="E79" s="13" t="inlineStr"/>
+      <c r="F79" s="13" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n">
+      <c r="A80" s="11" t="n">
         <v>1994</v>
       </c>
-      <c r="B80" s="13" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C80" s="13" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr"/>
-      <c r="E80" s="12" t="inlineStr"/>
-      <c r="F80" s="12" t="inlineStr"/>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr"/>
+      <c r="E80" s="13" t="inlineStr"/>
+      <c r="F80" s="13" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="n">
+      <c r="A81" s="11" t="n">
         <v>1995</v>
       </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>Edmonton, AB; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>Edmonton, AB; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr"/>
-      <c r="E81" s="12" t="inlineStr"/>
-      <c r="F81" s="12" t="inlineStr"/>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr"/>
+      <c r="E81" s="13" t="inlineStr"/>
+      <c r="F81" s="13" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="n">
+      <c r="A82" s="11" t="n">
         <v>1996</v>
       </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr"/>
-      <c r="E82" s="12" t="inlineStr"/>
-      <c r="F82" s="12" t="inlineStr"/>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr"/>
+      <c r="E82" s="13" t="inlineStr"/>
+      <c r="F82" s="13" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="n">
+      <c r="A83" s="11" t="n">
         <v>1997</v>
       </c>
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>Seattle, WA; OCR</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>Seattle, WA (58); OCR</t>
-        </is>
-      </c>
-      <c r="D83" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E83" s="12" t="inlineStr"/>
-      <c r="F83" s="12" t="inlineStr"/>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>Seattle, WA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Seattle, WA (58); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr"/>
+      <c r="F83" s="13" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="n">
+      <c r="A84" s="11" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>Guelph, ON; OCR</t>
-        </is>
-      </c>
-      <c r="C84" s="14" t="inlineStr">
-        <is>
-          <t>Guelph, ON (15); OCR</t>
-        </is>
-      </c>
-      <c r="D84" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E84" s="12" t="inlineStr"/>
-      <c r="F84" s="12" t="inlineStr"/>
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>Guelph, ON; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Guelph, ON (15); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr"/>
+      <c r="F84" s="13" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="n">
+      <c r="A85" s="11" t="n">
         <v>1999</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>University Park, PA; OCR</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>University Park, PA (57); OCR</t>
-        </is>
-      </c>
-      <c r="D85" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr"/>
-      <c r="F85" s="12" t="inlineStr"/>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>University Park, PA (57); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr"/>
+      <c r="F85" s="13" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>La Paz, Mexico; OCR</t>
-        </is>
-      </c>
-      <c r="C86" s="14" t="inlineStr">
-        <is>
-          <t>La Paz, Mexico (59); OCR</t>
-        </is>
-      </c>
-      <c r="D86" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr"/>
-      <c r="F86" s="12" t="inlineStr"/>
+      <c r="B86" s="15" t="inlineStr">
+        <is>
+          <t>La Paz, Mexico; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>La Paz, Mexico (59); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr"/>
+      <c r="F86" s="13" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="n">
+      <c r="A87" s="11" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>University Park, PA; OCR</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="inlineStr">
-        <is>
-          <t>University Park, PA (67); OCR</t>
-        </is>
-      </c>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="inlineStr"/>
-      <c r="F87" s="12" t="inlineStr"/>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>University Park, PA (67); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr"/>
+      <c r="F87" s="13" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="n">
+      <c r="A88" s="11" t="n">
         <v>2002</v>
       </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Kansas City, MO; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>Kansas City, MO; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E88" s="12" t="inlineStr"/>
-      <c r="F88" s="12" t="inlineStr"/>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr"/>
+      <c r="F88" s="13" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="n">
+      <c r="A89" s="11" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D89" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E89" s="12" t="inlineStr"/>
-      <c r="F89" s="12" t="inlineStr"/>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr"/>
+      <c r="F89" s="13" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="n">
+      <c r="A90" s="11" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>Norman, OK; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>Norman, OK; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E90" s="12" t="inlineStr"/>
-      <c r="F90" s="12" t="inlineStr"/>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr"/>
+      <c r="F90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="10" t="n">
+      <c r="A91" s="11" t="n">
         <v>2005</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>Tampa, FL; Ingested</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr">
+      <c r="C91" s="16" t="inlineStr">
         <is>
           <t>Tampa, FL (80); Ingested</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="inlineStr"/>
-      <c r="F91" s="12" t="inlineStr"/>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr"/>
+      <c r="F91" s="13" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="n">
+      <c r="A92" s="11" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D92" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E92" s="12" t="inlineStr"/>
-      <c r="F92" s="12" t="inlineStr"/>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr"/>
+      <c r="F92" s="13" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="n">
+      <c r="A93" s="11" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>St. Louis, MO; Ingested</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
+      <c r="C93" s="16" t="inlineStr">
         <is>
           <t>St. Louis, MO (155); Ingested</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="inlineStr"/>
-      <c r="F93" s="12" t="inlineStr"/>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="inlineStr"/>
+      <c r="F93" s="13" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="n">
+      <c r="A94" s="11" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>Montreal, PQ; Schedule</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>Montreal, PQ (193); Schedule</t>
-        </is>
-      </c>
-      <c r="D94" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E94" s="12" t="inlineStr"/>
-      <c r="F94" s="12" t="inlineStr"/>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Montreal, PQ; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>Montreal, PQ (193); Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr"/>
+      <c r="F94" s="13" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="n">
+      <c r="A95" s="11" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>Portland, OR; Ingested</t>
         </is>
       </c>
-      <c r="C95" s="15" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>Portland, OR (149); Ingested</t>
         </is>
       </c>
-      <c r="D95" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy (Ali archive)</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="inlineStr"/>
-      <c r="F95" s="12" t="inlineStr"/>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr"/>
+      <c r="F95" s="13" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="n">
+      <c r="A96" s="11" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>Providence, RI; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>Providence, RI; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>Galway; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr"/>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>Cairns; Missing</t>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="inlineStr">
+        <is>
+          <t>Galway; Hardcopy — Cat has hardcopy</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr"/>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Cairns; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="10" t="n">
+      <c r="A97" s="11" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" s="13" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C97" s="13" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D97" s="13" t="inlineStr">
-        <is>
-          <t>Berlin; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr"/>
-      <c r="F97" s="12" t="inlineStr"/>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>Berlin; Hardcopy — Cat has hardcopy</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="inlineStr"/>
+      <c r="F97" s="13" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="n">
+      <c r="A98" s="11" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="15" t="inlineStr">
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>Vancouver, BC; Ingested</t>
         </is>
       </c>
-      <c r="C98" s="15" t="inlineStr">
+      <c r="C98" s="16" t="inlineStr">
         <is>
           <t>Vancouver, BC (65); Ingested</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr">
-        <is>
-          <t>Milan; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E98" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F98" s="12" t="inlineStr"/>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>Milan; Hardcopy — Cat has hardcopy</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="n">
+      <c r="A99" s="11" t="n">
         <v>2013</v>
       </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D99" s="18" t="inlineStr">
-        <is>
-          <t>Plymouth; Digital</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr"/>
-      <c r="F99" s="12" t="inlineStr"/>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>Plymouth; Digital — abstract book held — ingest</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr"/>
+      <c r="F99" s="13" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n">
+      <c r="A100" s="11" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C100" s="13" t="inlineStr">
-        <is>
-          <t>Chattanooga, TN; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D100" s="13" t="inlineStr">
-        <is>
-          <t>Leeuwarden; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E100" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>Durban; Missing</t>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="inlineStr">
+        <is>
+          <t>Leeuwarden; Hardcopy — Cat has hardcopy</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Durban; Missing — find source</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="n">
+      <c r="A101" s="11" t="n">
         <v>2015</v>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="B101" s="16" t="inlineStr">
         <is>
           <t>Reno, NV; Ingested</t>
         </is>
       </c>
-      <c r="C101" s="15" t="inlineStr">
+      <c r="C101" s="16" t="inlineStr">
         <is>
           <t>Reno, NV (123); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
-        <is>
-          <t>Peniche; Digital</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr"/>
-      <c r="F101" s="12" t="inlineStr"/>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Peniche; Digital — abstract book held — ingest</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr"/>
+      <c r="F101" s="13" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n">
+      <c r="A102" s="11" t="n">
         <v>2016</v>
       </c>
-      <c r="B102" s="15" t="inlineStr">
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C102" s="15" t="inlineStr">
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>New Orleans, LA (240); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr">
-        <is>
-          <t>Bristol; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E102" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F102" s="12" t="inlineStr"/>
+      <c r="D102" s="14" t="inlineStr">
+        <is>
+          <t>Bristol; Hardcopy — Cat (Shark Trust) hosted — ask for print PDF</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="n">
+      <c r="A103" s="11" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="18" t="inlineStr">
-        <is>
-          <t>Austin, TX; Digital</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>Austin, TX; Digital</t>
-        </is>
-      </c>
-      <c r="D103" s="18" t="inlineStr">
-        <is>
-          <t>Amsterdam; Digital</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr"/>
-      <c r="F103" s="12" t="inlineStr"/>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Amsterdam; Programme — only programme held — abstract book needed</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr"/>
+      <c r="F103" s="13" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n">
+      <c r="A104" s="11" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="13" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C104" s="13" t="inlineStr">
-        <is>
-          <t>Rochester, NY; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D104" s="18" t="inlineStr">
-        <is>
-          <t>Peniche; Digital</t>
-        </is>
-      </c>
-      <c r="E104" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F104" s="15" t="inlineStr">
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Peniche; Missing — Cat: no hardcopy, likely online-only — find</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
         <is>
           <t>Joao Pessoa; Ingested</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="n">
+      <c r="A105" s="11" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="18" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Digital</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>Snowbird, UT; Digital</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>Rende; Hardcopy</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr"/>
-      <c r="F105" s="12" t="inlineStr"/>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>Rende; Hardcopy — Cat has hardcopy</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr"/>
+      <c r="F105" s="13" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="10" t="n">
+      <c r="A106" s="11" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy</t>
-        </is>
-      </c>
-      <c r="C106" s="13" t="inlineStr">
-        <is>
-          <t>?; Hardcopy</t>
-        </is>
-      </c>
-      <c r="D106" s="18" t="inlineStr">
-        <is>
-          <t>online (covid); Digital</t>
-        </is>
-      </c>
-      <c r="E106" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F106" s="12" t="inlineStr"/>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>online (covid); Missing — covid/online — find</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="10" t="n">
+      <c r="A107" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ; Schedule</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ (46); Schedule</t>
-        </is>
-      </c>
-      <c r="D107" s="18" t="inlineStr">
-        <is>
-          <t>Leiden; Digital</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr"/>
-      <c r="F107" s="12" t="inlineStr"/>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>Leiden; Programme — only programme held — abstract book needed</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr"/>
+      <c r="F107" s="13" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="n">
+      <c r="A108" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>Spokane, WA; Schedule</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>Spokane, WA (69); Schedule</t>
-        </is>
-      </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>Valencia (SI); Digital</t>
-        </is>
-      </c>
-      <c r="E108" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F108" s="15" t="inlineStr">
-        <is>
-          <t>Valencia; Ingested</t>
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>Spokane, WA; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>Valencia (=SI2022); Schedule — covered via SI2022 (schedule)</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>Valencia; Schedule — programme ingested (no bodies)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="n">
+      <c r="A109" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>Norfolk, VA; Schedule</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="inlineStr">
-        <is>
-          <t>Norfolk, VA (87); Schedule</t>
-        </is>
-      </c>
-      <c r="D109" s="18" t="inlineStr">
-        <is>
-          <t>Brighton; Digital</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="inlineStr"/>
-      <c r="F109" s="12" t="inlineStr"/>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Brighton; Programme — programme held; abstract book available — ask Cat</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr"/>
+      <c r="F109" s="13" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="10" t="n">
+      <c r="A110" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA; Schedule</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA (97); Schedule</t>
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>Thessaloniki; Digital</t>
-        </is>
-      </c>
-      <c r="E110" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F110" s="12" t="inlineStr"/>
+          <t>Thessaloniki; Pending — abstract book available — ask Cat</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="10" t="n">
+      <c r="A111" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="16" t="inlineStr">
-        <is>
-          <t>St. Paul, MN; Schedule</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>St. Paul, MN (68); Schedule</t>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies)</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
       <c r="D111" s="18" t="inlineStr">
         <is>
-          <t>Rotterdam; Digital</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr"/>
-      <c r="F111" s="12" t="inlineStr"/>
+          <t>Rotterdam; Pending — abstract book available — ask Cat</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr"/>
+      <c r="F111" s="13" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="n">
+      <c r="A112" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="18" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Digital</t>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
         </is>
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>online; Digital</t>
-        </is>
-      </c>
-      <c r="E112" s="17" t="inlineStr">
-        <is>
-          <t>?; Pending (Brit)</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
+          <t>online; Pending — will be digital</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Brit collating (council approval)</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr">
         <is>
           <t>Colombo; Ingested</t>
         </is>
@@ -3098,7 +3120,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,9 +155,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1121,7 +1118,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA not yet ingested. SI2022 Valencia PDF received (Digital).</t>
+          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14); 2024/2025 PDFs corrupt (await clean copies from Cat). SI2022 Valencia PDF received (Digital).</t>
         </is>
       </c>
     </row>
@@ -2558,9 +2555,9 @@
           <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D90" s="14" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>London; Ingested — 55 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr"/>
@@ -2716,9 +2713,9 @@
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D97" s="14" t="inlineStr">
-        <is>
-          <t>Berlin; Hardcopy — Cat has hardcopy</t>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr"/>
@@ -2764,9 +2761,9 @@
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D99" s="19" t="inlineStr">
-        <is>
-          <t>Plymouth; Digital — abstract book held — ingest</t>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr"/>
@@ -2786,9 +2783,9 @@
           <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D100" s="14" t="inlineStr">
-        <is>
-          <t>Leeuwarden; Hardcopy — Cat has hardcopy</t>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E100" s="18" t="inlineStr">
@@ -2818,7 +2815,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t>Peniche; Digital — abstract book held — ingest</t>
+          <t>Peniche; Programme — 2-page programme only (0 abstracts) — abstract book needed</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr"/>
@@ -2838,9 +2835,9 @@
           <t>New Orleans, LA (240); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="14" t="inlineStr">
-        <is>
-          <t>Bristol; Hardcopy — Cat (Shark Trust) hosted — ask for print PDF</t>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E102" s="18" t="inlineStr">
@@ -2854,19 +2851,19 @@
       <c r="A103" s="11" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="20" t="inlineStr">
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C103" s="20" t="inlineStr">
+      <c r="C103" s="19" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
-        <is>
-          <t>Amsterdam; Programme — only programme held — abstract book needed</t>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>Amsterdam; Ingested — 62 talks, programme/no bodies (Fable)</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr"/>
@@ -2886,9 +2883,9 @@
           <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>Peniche; Missing — Cat: no hardcopy, likely online-only — find</t>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E104" s="18" t="inlineStr">
@@ -2906,19 +2903,19 @@
       <c r="A105" s="11" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="20" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C105" s="20" t="inlineStr">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D105" s="14" t="inlineStr">
-        <is>
-          <t>Rende; Hardcopy — Cat has hardcopy</t>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr"/>
@@ -2964,7 +2961,7 @@
           <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D107" s="20" t="inlineStr">
+      <c r="D107" s="19" t="inlineStr">
         <is>
           <t>Leiden; Programme — only programme held — abstract book needed</t>
         </is>
@@ -3016,9 +3013,9 @@
           <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D109" s="20" t="inlineStr">
-        <is>
-          <t>Brighton; Programme — programme held; abstract book available — ask Cat</t>
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>Brighton; Ingested — oral 64 + poster 34 = 98 abstracts (Fable)</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr"/>
@@ -3040,7 +3037,7 @@
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>Thessaloniki; Pending — abstract book available — ask Cat</t>
+          <t>Thessaloniki; Pending — PDF corrupt — need clean copy from Cat</t>
         </is>
       </c>
       <c r="E110" s="18" t="inlineStr">
@@ -3066,7 +3063,7 @@
       </c>
       <c r="D111" s="18" t="inlineStr">
         <is>
-          <t>Rotterdam; Pending — abstract book available — ask Cat</t>
+          <t>Rotterdam; Pending — PDF corrupt — need clean copy from Cat</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr"/>
@@ -3076,12 +3073,12 @@
       <c r="A112" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="20" t="inlineStr">
+      <c r="B112" s="19" t="inlineStr">
         <is>
           <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
         </is>
       </c>
-      <c r="C112" s="20" t="inlineStr">
+      <c r="C112" s="19" t="inlineStr">
         <is>
           <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
         </is>
@@ -3120,7 +3117,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -151,13 +151,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2523,14 +2523,14 @@
       <c r="A89" s="11" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -2545,14 +2545,14 @@
       <c r="A90" s="11" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="14" t="inlineStr">
-        <is>
-          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr">
-        <is>
-          <t>Norman, OK; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
@@ -2633,14 +2633,14 @@
       <c r="A94" s="11" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Montreal, PQ; Schedule — programme ingested (no abstract bodies)</t>
-        </is>
-      </c>
-      <c r="C94" s="17" t="inlineStr">
-        <is>
-          <t>Montreal, PQ (193); Schedule — programme ingested (no abstract bodies)</t>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Montreal, PQ; Ingested</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
@@ -2740,7 +2740,7 @@
           <t>Milan; Hardcopy — Cat has hardcopy</t>
         </is>
       </c>
-      <c r="E98" s="18" t="inlineStr">
+      <c r="E98" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2788,7 +2788,7 @@
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E100" s="18" t="inlineStr">
+      <c r="E100" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2813,7 +2813,7 @@
           <t>Reno, NV (123); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="19" t="inlineStr">
+      <c r="D101" s="18" t="inlineStr">
         <is>
           <t>Peniche; Programme — 2-page programme only (0 abstracts) — abstract book needed</t>
         </is>
@@ -2840,7 +2840,7 @@
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="18" t="inlineStr">
+      <c r="E102" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2851,12 +2851,12 @@
       <c r="A103" s="11" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="19" t="inlineStr">
+      <c r="B103" s="18" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
+      <c r="C103" s="18" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
@@ -2888,7 +2888,7 @@
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="18" t="inlineStr">
+      <c r="E104" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2903,12 +2903,12 @@
       <c r="A105" s="11" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B105" s="18" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr">
+      <c r="C105" s="18" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
@@ -2940,7 +2940,7 @@
           <t>online (covid); Missing — covid/online — find</t>
         </is>
       </c>
-      <c r="E106" s="18" t="inlineStr">
+      <c r="E106" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2951,17 +2951,17 @@
       <c r="A107" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="17" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="C107" s="17" t="inlineStr">
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D107" s="19" t="inlineStr">
+      <c r="D107" s="18" t="inlineStr">
         <is>
           <t>Leiden; Programme — only programme held — abstract book needed</t>
         </is>
@@ -2973,27 +2973,27 @@
       <c r="A108" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="17" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>Spokane, WA; Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="C108" s="17" t="inlineStr">
+      <c r="C108" s="19" t="inlineStr">
         <is>
           <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D108" s="17" t="inlineStr">
+      <c r="D108" s="19" t="inlineStr">
         <is>
           <t>Valencia (=SI2022); Schedule — covered via SI2022 (schedule)</t>
         </is>
       </c>
-      <c r="E108" s="18" t="inlineStr">
+      <c r="E108" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
       </c>
-      <c r="F108" s="17" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>Valencia; Schedule — programme ingested (no bodies)</t>
         </is>
@@ -3003,12 +3003,12 @@
       <c r="A109" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="17" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="C109" s="17" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies)</t>
         </is>
@@ -3025,22 +3025,22 @@
       <c r="A110" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="17" t="inlineStr">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="C110" s="17" t="inlineStr">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D110" s="18" t="inlineStr">
+      <c r="D110" s="17" t="inlineStr">
         <is>
           <t>Thessaloniki; Pending — PDF corrupt — need clean copy from Cat</t>
         </is>
       </c>
-      <c r="E110" s="18" t="inlineStr">
+      <c r="E110" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -3051,17 +3051,17 @@
       <c r="A111" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="17" t="inlineStr">
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="C111" s="17" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
         <is>
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies)</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
+      <c r="D111" s="17" t="inlineStr">
         <is>
           <t>Rotterdam; Pending — PDF corrupt — need clean copy from Cat</t>
         </is>
@@ -3073,22 +3073,22 @@
       <c r="A112" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="19" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Programme — image-only programme — needs OCR; abstract book needed</t>
-        </is>
-      </c>
-      <c r="D112" s="18" t="inlineStr">
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Programme — schedule-only programme (OCR text layer OK, not yet parsed) — abstract book needed</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Programme — schedule-only programme (OCR text layer OK, not yet parsed) — abstract book needed</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="inlineStr">
         <is>
           <t>online; Pending — will be digital</t>
         </is>
       </c>
-      <c r="E112" s="18" t="inlineStr">
+      <c r="E112" s="17" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -142,13 +142,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,12 +269,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$B$3:$G$3</f>
+              <f>'Dashboard'!$B$3:$H$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$39:$G$39</f>
+              <f>'Dashboard'!$B$39:$H$39</f>
             </numRef>
           </val>
         </ser>
@@ -536,6 +536,38 @@
           <val>
             <numRef>
               <f>'Dashboard'!$G$4:$G$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!H3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$4:$A$38</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$H$4:$H$38</f>
             </numRef>
           </val>
         </ser>
@@ -942,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1104,40 +1136,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans will upgrade these.</t>
+          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- No abstracts collected pre-1992 (Carylanne's archive starts 1992) → 1916-1991 show host city but 'Missing'.</t>
+          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14); 2024/2025 PDFs corrupt (await clean copies from Cat). SI2022 Valencia PDF received (Digital).</t>
+          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
+          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14) and merged into the main DB 2026-08-25; 2024/2025 PDFs corrupt (await clean copies from Cat). SI2022 Valencia schedule ingested.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>- Blank/unshaded cell = no conference that year for that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>- Per-society counts &amp; trends: see the Dashboard tab.</t>
         </is>
@@ -2180,9 +2219,9 @@
           <t>Knoxville, TN; Missing</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>Knoxville, TN; Missing</t>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Knoxville, TN (26); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr"/>
@@ -2198,9 +2237,9 @@
           <t>Victoria, BC; Missing</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>Victoria, BC; Missing</t>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Victoria, BC (35); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr"/>
@@ -2216,9 +2255,9 @@
           <t>Albany, NY; Missing</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>Albany, NY; Missing</t>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Albany, NY (33); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr"/>
@@ -2234,9 +2273,9 @@
           <t>Ann Arbor, MI; Missing</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI; Missing</t>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr"/>
@@ -2252,9 +2291,9 @@
           <t>San Francisco, CA; Missing</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco, CA; Missing</t>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr"/>
@@ -2270,9 +2309,9 @@
           <t>Charleston, SC; Missing</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
-        <is>
-          <t>Charleston, SC; Missing</t>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Charleston, SC (47); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr"/>
@@ -2288,9 +2327,9 @@
           <t>New York, NY; Missing</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>New York, NY; Missing</t>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>New York, NY (34); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr"/>
@@ -2301,14 +2340,14 @@
       <c r="A78" s="11" t="n">
         <v>1992</v>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B78" s="15" t="inlineStr">
         <is>
           <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Champaign-Urbana, IL; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+          <t>Champaign-Urbana, IL (41); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr"/>
@@ -2319,14 +2358,14 @@
       <c r="A79" s="11" t="n">
         <v>1993</v>
       </c>
-      <c r="B79" s="14" t="inlineStr">
+      <c r="B79" s="15" t="inlineStr">
         <is>
           <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>Austin, TX; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+          <t>Austin, TX (45); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr"/>
@@ -2337,14 +2376,14 @@
       <c r="A80" s="11" t="n">
         <v>1994</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B80" s="15" t="inlineStr">
         <is>
           <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+          <t>Los Angeles, CA (50); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr"/>
@@ -2355,14 +2394,14 @@
       <c r="A81" s="11" t="n">
         <v>1995</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B81" s="15" t="inlineStr">
         <is>
           <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>Edmonton, AB; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+          <t>Edmonton, AB (46); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr"/>
@@ -2373,14 +2412,14 @@
       <c r="A82" s="11" t="n">
         <v>1996</v>
       </c>
-      <c r="B82" s="14" t="inlineStr">
+      <c r="B82" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
+          <t>New Orleans, LA (98); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr"/>
@@ -2391,17 +2430,17 @@
       <c r="A83" s="11" t="n">
         <v>1997</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>Seattle, WA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>Seattle, WA (58); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Seattle, WA (68); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2413,17 +2452,17 @@
       <c r="A84" s="11" t="n">
         <v>1998</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>Guelph, ON; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Guelph, ON (15); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Guelph, ON (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2435,17 +2474,17 @@
       <c r="A85" s="11" t="n">
         <v>1999</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>University Park, PA (57); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>University Park, PA (78); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2457,17 +2496,17 @@
       <c r="A86" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="B86" s="15" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>La Paz, Mexico; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>La Paz, Mexico (59); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
-        </is>
-      </c>
-      <c r="D86" s="14" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>La Paz, Mexico (134); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2479,17 +2518,17 @@
       <c r="A87" s="11" t="n">
         <v>2001</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>University Park, PA; OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
-        <is>
-          <t>University Park, PA (67); OCR — degraded scan (needs_review) — flatbed re-scan planned</t>
-        </is>
-      </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>University Park, PA (84); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2501,17 +2540,17 @@
       <c r="A88" s="11" t="n">
         <v>2002</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B88" s="15" t="inlineStr">
         <is>
           <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Kansas City, MO; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
-        </is>
-      </c>
-      <c r="D88" s="14" t="inlineStr">
+          <t>Kansas City, MO (27); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2523,17 +2562,17 @@
       <c r="A89" s="11" t="n">
         <v>2003</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>Manaus, Brazil; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Manaus, Brazil (82); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2545,17 +2584,17 @@
       <c r="A90" s="11" t="n">
         <v>2004</v>
       </c>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>Norman, OK; OCR — degraded phone scan — 0 abstracts recovered — flatbed re-scan needed (Carylanne)</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Norman, OK (59); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="inlineStr">
         <is>
           <t>London; Ingested — 55 abstracts (Fable)</t>
         </is>
@@ -2567,17 +2606,17 @@
       <c r="A91" s="11" t="n">
         <v>2005</v>
       </c>
-      <c r="B91" s="16" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>Tampa, FL; Ingested</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>Tampa, FL (80); Ingested</t>
-        </is>
-      </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Tampa, FL (158); Ingested — AES abstracts from elasmo.org (full bodies)</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2589,17 +2628,17 @@
       <c r="A92" s="11" t="n">
         <v>2006</v>
       </c>
-      <c r="B92" s="14" t="inlineStr">
+      <c r="B92" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C92" s="15" t="inlineStr">
         <is>
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D92" s="14" t="inlineStr">
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2611,17 +2650,17 @@
       <c r="A93" s="11" t="n">
         <v>2007</v>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="14" t="inlineStr">
         <is>
           <t>St. Louis, MO; Ingested</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
         <is>
           <t>St. Louis, MO (155); Ingested</t>
         </is>
       </c>
-      <c r="D93" s="14" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2633,17 +2672,17 @@
       <c r="A94" s="11" t="n">
         <v>2008</v>
       </c>
-      <c r="B94" s="16" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>Montreal, PQ; Ingested</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
-      <c r="D94" s="14" t="inlineStr">
+      <c r="D94" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2655,17 +2694,17 @@
       <c r="A95" s="11" t="n">
         <v>2009</v>
       </c>
-      <c r="B95" s="16" t="inlineStr">
+      <c r="B95" s="14" t="inlineStr">
         <is>
           <t>Portland, OR; Ingested</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>Portland, OR (149); Ingested</t>
         </is>
       </c>
-      <c r="D95" s="14" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
         </is>
@@ -2677,17 +2716,17 @@
       <c r="A96" s="11" t="n">
         <v>2010</v>
       </c>
-      <c r="B96" s="14" t="inlineStr">
+      <c r="B96" s="15" t="inlineStr">
         <is>
           <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C96" s="14" t="inlineStr">
+      <c r="C96" s="15" t="inlineStr">
         <is>
           <t>Providence, RI; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D96" s="14" t="inlineStr">
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>Galway; Hardcopy — Cat has hardcopy</t>
         </is>
@@ -2703,17 +2742,17 @@
       <c r="A97" s="11" t="n">
         <v>2011</v>
       </c>
-      <c r="B97" s="14" t="inlineStr">
+      <c r="B97" s="15" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C97" s="14" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
         <is>
           <t>Minneapolis, MN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D97" s="16" t="inlineStr">
+      <c r="D97" s="14" t="inlineStr">
         <is>
           <t>Berlin; Ingested — 58 abstracts (Fable)</t>
         </is>
@@ -2725,17 +2764,17 @@
       <c r="A98" s="11" t="n">
         <v>2012</v>
       </c>
-      <c r="B98" s="16" t="inlineStr">
+      <c r="B98" s="14" t="inlineStr">
         <is>
           <t>Vancouver, BC; Ingested</t>
         </is>
       </c>
-      <c r="C98" s="16" t="inlineStr">
+      <c r="C98" s="14" t="inlineStr">
         <is>
           <t>Vancouver, BC (65); Ingested</t>
         </is>
       </c>
-      <c r="D98" s="14" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>Milan; Hardcopy — Cat has hardcopy</t>
         </is>
@@ -2751,17 +2790,17 @@
       <c r="A99" s="11" t="n">
         <v>2013</v>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B99" s="15" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C99" s="14" t="inlineStr">
+      <c r="C99" s="15" t="inlineStr">
         <is>
           <t>Albuquerque, NM; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D99" s="16" t="inlineStr">
+      <c r="D99" s="14" t="inlineStr">
         <is>
           <t>Plymouth; Ingested — 93 abstracts (Fable)</t>
         </is>
@@ -2773,17 +2812,17 @@
       <c r="A100" s="11" t="n">
         <v>2014</v>
       </c>
-      <c r="B100" s="14" t="inlineStr">
+      <c r="B100" s="15" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C100" s="14" t="inlineStr">
+      <c r="C100" s="15" t="inlineStr">
         <is>
           <t>Chattanooga, TN; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D100" s="16" t="inlineStr">
+      <c r="D100" s="14" t="inlineStr">
         <is>
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
@@ -2803,12 +2842,12 @@
       <c r="A101" s="11" t="n">
         <v>2015</v>
       </c>
-      <c r="B101" s="16" t="inlineStr">
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>Reno, NV; Ingested</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
         <is>
           <t>Reno, NV (123); Ingested</t>
         </is>
@@ -2825,17 +2864,17 @@
       <c r="A102" s="11" t="n">
         <v>2016</v>
       </c>
-      <c r="B102" s="16" t="inlineStr">
+      <c r="B102" s="14" t="inlineStr">
         <is>
           <t>New Orleans, LA; Ingested</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C102" s="14" t="inlineStr">
         <is>
           <t>New Orleans, LA (240); Ingested</t>
         </is>
       </c>
-      <c r="D102" s="16" t="inlineStr">
+      <c r="D102" s="14" t="inlineStr">
         <is>
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
@@ -2861,7 +2900,7 @@
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D103" s="16" t="inlineStr">
+      <c r="D103" s="14" t="inlineStr">
         <is>
           <t>Amsterdam; Ingested — 62 talks, programme/no bodies (Fable)</t>
         </is>
@@ -2873,17 +2912,17 @@
       <c r="A104" s="11" t="n">
         <v>2018</v>
       </c>
-      <c r="B104" s="14" t="inlineStr">
+      <c r="B104" s="15" t="inlineStr">
         <is>
           <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C104" s="14" t="inlineStr">
+      <c r="C104" s="15" t="inlineStr">
         <is>
           <t>Rochester, NY; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D104" s="16" t="inlineStr">
+      <c r="D104" s="14" t="inlineStr">
         <is>
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
@@ -2893,7 +2932,7 @@
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
       </c>
-      <c r="F104" s="16" t="inlineStr">
+      <c r="F104" s="14" t="inlineStr">
         <is>
           <t>Joao Pessoa; Ingested</t>
         </is>
@@ -2913,7 +2952,7 @@
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
+      <c r="D105" s="14" t="inlineStr">
         <is>
           <t>Rende; Ingested — 136 abstracts (Fable)</t>
         </is>
@@ -2925,12 +2964,12 @@
       <c r="A106" s="11" t="n">
         <v>2020</v>
       </c>
-      <c r="B106" s="14" t="inlineStr">
+      <c r="B106" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="C106" s="14" t="inlineStr">
+      <c r="C106" s="15" t="inlineStr">
         <is>
           <t>?; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
@@ -2953,12 +2992,12 @@
       </c>
       <c r="B107" s="19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies)</t>
+          <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies)</t>
+          <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D107" s="18" t="inlineStr">
@@ -2975,12 +3014,12 @@
       </c>
       <c r="B108" s="19" t="inlineStr">
         <is>
-          <t>Spokane, WA; Schedule — programme ingested (no abstract bodies)</t>
+          <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies)</t>
+          <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D108" s="19" t="inlineStr">
@@ -3005,15 +3044,15 @@
       </c>
       <c r="B109" s="19" t="inlineStr">
         <is>
-          <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies)</t>
+          <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="C109" s="19" t="inlineStr">
         <is>
-          <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies)</t>
-        </is>
-      </c>
-      <c r="D109" s="16" t="inlineStr">
+          <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>Brighton; Ingested — oral 64 + poster 34 = 98 abstracts (Fable)</t>
         </is>
@@ -3027,12 +3066,12 @@
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies)</t>
+          <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies)</t>
+          <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D110" s="17" t="inlineStr">
@@ -3053,12 +3092,12 @@
       </c>
       <c r="B111" s="19" t="inlineStr">
         <is>
-          <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies)</t>
+          <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="C111" s="19" t="inlineStr">
         <is>
-          <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies)</t>
+          <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D111" s="17" t="inlineStr">
@@ -3093,7 +3132,7 @@
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
       </c>
-      <c r="F112" s="16" t="inlineStr">
+      <c r="F112" s="14" t="inlineStr">
         <is>
           <t>Colombo; Ingested</t>
         </is>
@@ -3110,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3156,6 +3195,11 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
+          <t>EEA</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
           <t>SI</t>
         </is>
       </c>
@@ -3165,7 +3209,7 @@
         <v>1992</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -3180,6 +3224,9 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3188,7 +3235,7 @@
         <v>1993</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -3203,6 +3250,9 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3211,7 +3261,7 @@
         <v>1994</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3226,6 +3276,9 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3234,7 +3287,7 @@
         <v>1995</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3249,6 +3302,9 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3257,7 +3313,7 @@
         <v>1996</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -3272,6 +3328,9 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3280,7 +3339,7 @@
         <v>1997</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -3295,6 +3354,9 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3303,7 +3365,7 @@
         <v>1998</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -3318,6 +3380,9 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3326,7 +3391,7 @@
         <v>1999</v>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -3341,6 +3406,9 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3349,7 +3417,7 @@
         <v>2000</v>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -3364,6 +3432,9 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3372,7 +3443,7 @@
         <v>2001</v>
       </c>
       <c r="B13" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -3387,6 +3458,9 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3395,7 +3469,7 @@
         <v>2002</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -3410,6 +3484,9 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3418,7 +3495,7 @@
         <v>2003</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -3433,6 +3510,9 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3441,7 +3521,7 @@
         <v>2004</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -3456,6 +3536,9 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
+        <v>55</v>
+      </c>
+      <c r="H16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3464,7 +3547,7 @@
         <v>2005</v>
       </c>
       <c r="B17" t="n">
-        <v>81</v>
+        <v>158</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -3479,6 +3562,9 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3504,6 +3590,9 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3527,6 +3616,9 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3550,6 +3642,9 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3573,6 +3668,9 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3596,6 +3694,9 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3617,6 +3718,9 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>58</v>
+      </c>
+      <c r="H23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3642,6 +3746,9 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3663,6 +3770,9 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>93</v>
+      </c>
+      <c r="H25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3686,6 +3796,9 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>61</v>
+      </c>
+      <c r="H26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3711,6 +3824,9 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3732,6 +3848,9 @@
         <v>27</v>
       </c>
       <c r="G28" t="n">
+        <v>93</v>
+      </c>
+      <c r="H28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3755,6 +3874,9 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
+        <v>62</v>
+      </c>
+      <c r="H29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3778,6 +3900,9 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>75</v>
+      </c>
+      <c r="H30" t="n">
         <v>427</v>
       </c>
     </row>
@@ -3801,6 +3926,9 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
+        <v>136</v>
+      </c>
+      <c r="H31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3826,6 +3954,9 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3849,6 +3980,9 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3870,6 +4004,9 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
         <v>89</v>
       </c>
     </row>
@@ -3893,6 +4030,9 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
+        <v>98</v>
+      </c>
+      <c r="H35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3918,6 +4058,9 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3941,6 +4084,9 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3962,6 +4108,9 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>1001</v>
       </c>
     </row>
@@ -3972,7 +4121,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>1654</v>
+        <v>2346</v>
       </c>
       <c r="C39" s="1" t="n">
         <v>1984</v>
@@ -3987,6 +4136,9 @@
         <v>99</v>
       </c>
       <c r="G39" s="1" t="n">
+        <v>731</v>
+      </c>
+      <c r="H39" s="1" t="n">
         <v>1517</v>
       </c>
     </row>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>New Orleans, LA (240); Ingested</t>
+          <t>New Orleans, LA (251); Ingested</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -3112,14 +3112,14 @@
       <c r="A112" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="18" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Programme — schedule-only programme (OCR text layer OK, not yet parsed) — abstract book needed</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>New Orleans, LA; Programme — schedule-only programme (OCR text layer OK, not yet parsed) — abstract book needed</t>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>New Orleans, LA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>New Orleans, LA (61); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
       <c r="D112" s="17" t="inlineStr">
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>2006</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>2007</v>
       </c>
       <c r="B19" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C19" t="n">
         <v>427</v>
@@ -3625,7 +3625,7 @@
         <v>2008</v>
       </c>
       <c r="B20" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C20" t="n">
         <v>215</v>
@@ -3651,7 +3651,7 @@
         <v>2009</v>
       </c>
       <c r="B21" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C21" t="n">
         <v>454</v>
@@ -3677,7 +3677,7 @@
         <v>2010</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>2011</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>2012</v>
       </c>
       <c r="B24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>2013</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -3781,7 +3781,7 @@
         <v>2014</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" t="n">
         <v>285</v>
@@ -3833,19 +3833,19 @@
         <v>2016</v>
       </c>
       <c r="B28" t="n">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="C28" t="n">
-        <v>375</v>
+        <v>137</v>
       </c>
       <c r="D28" t="n">
-        <v>204</v>
+        <v>39</v>
       </c>
       <c r="E28" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>93</v>
@@ -3859,7 +3859,7 @@
         <v>2017</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         <v>2018</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>2019</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -4093,19 +4093,19 @@
         <v>2026</v>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -4121,19 +4121,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2346</v>
+        <v>2282</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>1984</v>
+        <v>1767</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>998</v>
+        <v>845</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>228</v>
+        <v>329</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>731</v>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -3342,10 +3342,10 @@
         <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3368,16 +3368,16 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -3394,16 +3394,16 @@
         <v>78</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3420,16 +3420,16 @@
         <v>134</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -3446,10 +3446,10 @@
         <v>84</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>55</v>
@@ -3547,19 +3547,19 @@
         <v>2005</v>
       </c>
       <c r="B17" t="n">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="E17" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>193</v>
       </c>
       <c r="C20" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="D20" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E20" t="n">
         <v>27</v>
@@ -3654,7 +3654,7 @@
         <v>149</v>
       </c>
       <c r="C21" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D21" t="n">
         <v>215</v>
@@ -3663,7 +3663,7 @@
         <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3810,7 +3810,7 @@
         <v>123</v>
       </c>
       <c r="C27" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D27" t="n">
         <v>130</v>
@@ -3833,19 +3833,19 @@
         <v>2016</v>
       </c>
       <c r="B28" t="n">
-        <v>162</v>
+        <v>245</v>
       </c>
       <c r="C28" t="n">
-        <v>137</v>
+        <v>443</v>
       </c>
       <c r="D28" t="n">
-        <v>39</v>
+        <v>258</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
       </c>
       <c r="F28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G28" t="n">
         <v>93</v>
@@ -4121,19 +4121,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2282</v>
+        <v>2399</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>1767</v>
+        <v>3731</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>845</v>
+        <v>2088</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>731</v>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -3345,7 +3345,7 @@
         <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3397,7 +3397,7 @@
         <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3420,10 +3420,10 @@
         <v>134</v>
       </c>
       <c r="C12" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>199</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3550,10 +3550,10 @@
         <v>192</v>
       </c>
       <c r="C17" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D17" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E17" t="n">
         <v>36</v>
@@ -3839,7 +3839,7 @@
         <v>443</v>
       </c>
       <c r="D28" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
@@ -4124,10 +4124,10 @@
         <v>2399</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>3731</v>
+        <v>3735</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>334</v>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>Reno, NV (123); Ingested</t>
+          <t>Reno, NV (128); Ingested</t>
         </is>
       </c>
       <c r="D101" s="18" t="inlineStr">
@@ -3550,10 +3550,10 @@
         <v>192</v>
       </c>
       <c r="C17" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D17" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E17" t="n">
         <v>36</v>
@@ -3807,19 +3807,19 @@
         <v>2015</v>
       </c>
       <c r="B27" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C27" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="D27" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -3836,10 +3836,10 @@
         <v>245</v>
       </c>
       <c r="C28" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D28" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E28" t="n">
         <v>97</v>
@@ -4121,19 +4121,19 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>3735</v>
+        <v>3756</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>2094</v>
+        <v>2108</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>731</v>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +158,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1157,7 +1160,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14) and merged into the main DB 2026-08-25; 2024/2025 PDFs corrupt (await clean copies from Cat). SI2022 Valencia schedule ingested.</t>
+          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14) and merged into the main DB 2026-08-25; 2024 abstract book received clean 2026-08-27 (queued for extraction); 2025 abstract book still corrupt — working copy needed from Cat. SI2022 Valencia schedule ingested.</t>
         </is>
       </c>
     </row>
@@ -3074,9 +3077,9 @@
           <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D110" s="17" t="inlineStr">
-        <is>
-          <t>Thessaloniki; Pending — PDF corrupt — need clean copy from Cat</t>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27 — queued for extraction</t>
         </is>
       </c>
       <c r="E110" s="17" t="inlineStr">
@@ -3100,9 +3103,9 @@
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D111" s="17" t="inlineStr">
-        <is>
-          <t>Rotterdam; Pending — PDF corrupt — need clean copy from Cat</t>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>Rotterdam; Programme — programme held; abstract book still corrupt — working copy needed from Cat</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr"/>
@@ -3156,7 +3159,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Conference abstract coverage — dashboard</t>
         </is>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -151,6 +151,9 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -158,9 +161,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1160,7 +1160,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- EEA 2010-2026 from Cat Gordon (Shark Trust); pre-2010 in Ali's archive. EEA 2004-2019 + 2023 ingested via Fable (731 abstracts, 2026-08-14) and merged into the main DB 2026-08-25; 2024 abstract book received clean 2026-08-27 (queued for extraction); 2025 abstract book still corrupt — working copy needed from Cat. SI2022 Valencia schedule ingested.</t>
+          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
         </is>
       </c>
     </row>
@@ -2443,9 +2443,9 @@
           <t>Seattle, WA (68); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>?; Missing — EEA conferences 1-5, no known source</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr"/>
@@ -2465,9 +2465,9 @@
           <t>Guelph, ON (63); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>?; Missing — EEA conferences 1-5, no known source</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr"/>
@@ -2487,9 +2487,9 @@
           <t>University Park, PA (78); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>?; Missing — EEA conferences 1-5, no known source</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr"/>
@@ -2509,9 +2509,9 @@
           <t>La Paz, Mexico (134); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>?; Missing — EEA conferences 1-5, no known source</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr"/>
@@ -2531,9 +2531,9 @@
           <t>University Park, PA (84); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D87" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>?; Missing — EEA conferences 1-5, no known source</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr"/>
@@ -2553,9 +2553,9 @@
           <t>Kansas City, MO (27); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>Cardiff; Digital — abstract booklet (Word) from Cat 2026-08-27 — queued for extraction</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr"/>
@@ -2575,9 +2575,9 @@
           <t>Manaus, Brazil (82); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr"/>
@@ -2619,9 +2619,9 @@
           <t>Tampa, FL (158); Ingested — AES abstracts from elasmo.org (full bodies)</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr"/>
@@ -2641,9 +2641,9 @@
           <t>New Orleans, LA; Hardcopy — Carylanne has hardcopy (1992-2024) — get abstract book</t>
         </is>
       </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr"/>
@@ -2663,9 +2663,9 @@
           <t>St. Louis, MO (155); Ingested</t>
         </is>
       </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr"/>
@@ -2685,9 +2685,9 @@
           <t>Montreal, PQ (193); Ingested</t>
         </is>
       </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr"/>
@@ -2707,9 +2707,9 @@
           <t>Portland, OR (149); Ingested</t>
         </is>
       </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>?; Hardcopy — Ali's archive (back mid-Aug)</t>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Galway; Hardcopy — Cat has hardcopy</t>
+          <t>Galway; Hardcopy — Cat has hardcopy but no scanning capacity — digital needed from IEG (Ireland)</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>Milan; Hardcopy — Cat has hardcopy</t>
-        </is>
-      </c>
-      <c r="E98" s="17" t="inlineStr">
+          <t>Milan; Hardcopy — Cat has hardcopy but no scanning capacity — digital needed from GRIS (Italy)</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2830,7 +2830,7 @@
           <t>Leeuwarden; Ingested — 61 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E100" s="17" t="inlineStr">
+      <c r="E100" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2855,9 +2855,9 @@
           <t>Reno, NV (128); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
-        <is>
-          <t>Peniche; Programme — 2-page programme only (0 abstracts) — abstract book needed</t>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Peniche; Programme — 2-page programme only; Cat has hardcopy but no scanning capacity — abstract book needed from APECE (Portugal)</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
           <t>Bristol; Ingested — 93 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E102" s="17" t="inlineStr">
+      <c r="E102" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2893,19 +2893,19 @@
       <c r="A103" s="11" t="n">
         <v>2017</v>
       </c>
-      <c r="B103" s="18" t="inlineStr">
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C103" s="18" t="inlineStr">
+      <c r="C103" s="19" t="inlineStr">
         <is>
           <t>Austin, TX; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="D103" s="14" t="inlineStr">
-        <is>
-          <t>Amsterdam; Ingested — 62 talks, programme/no bodies (Fable)</t>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat has hardcopy but no scanning capacity — abstract book needed from NEV</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
           <t>Peniche; Ingested — 75 abstracts (Fable)</t>
         </is>
       </c>
-      <c r="E104" s="17" t="inlineStr">
+      <c r="E104" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2945,12 +2945,12 @@
       <c r="A105" s="11" t="n">
         <v>2019</v>
       </c>
-      <c r="B105" s="18" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
       </c>
-      <c r="C105" s="18" t="inlineStr">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>Snowbird, UT; Programme — grid programme only — abstract book needed (Carylanne)</t>
         </is>
@@ -2982,7 +2982,7 @@
           <t>online (covid); Missing — covid/online — find</t>
         </is>
       </c>
-      <c r="E106" s="17" t="inlineStr">
+      <c r="E106" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -2993,19 +2993,19 @@
       <c r="A107" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>Phoenix, AZ; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C107" s="19" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>Phoenix, AZ (46); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D107" s="18" t="inlineStr">
-        <is>
-          <t>Leiden; Programme — only programme held — abstract book needed</t>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>Leiden; Programme — programme only — abstract book needed from NEV</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr"/>
@@ -3015,29 +3015,29 @@
       <c r="A108" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B108" s="19" t="inlineStr">
+      <c r="B108" s="20" t="inlineStr">
         <is>
           <t>Spokane, WA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C108" s="19" t="inlineStr">
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>Spokane, WA (69); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D108" s="19" t="inlineStr">
-        <is>
-          <t>Valencia (=SI2022); Schedule — covered via SI2022 (schedule)</t>
-        </is>
-      </c>
-      <c r="E108" s="17" t="inlineStr">
+      <c r="D108" s="17" t="inlineStr">
+        <is>
+          <t>Valencia (=SI2022); Digital — full SI2022 abstract book from Cat 2026-08-27 — queued for extraction</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
       </c>
-      <c r="F108" s="19" t="inlineStr">
-        <is>
-          <t>Valencia; Schedule — programme ingested (no bodies)</t>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>Valencia; Digital — full abstract book received 2026-08-27 — queued (schedule already ingested)</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3045,12 @@
       <c r="A109" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B109" s="19" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>Norfolk, VA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C109" s="19" t="inlineStr">
+      <c r="C109" s="20" t="inlineStr">
         <is>
           <t>Norfolk, VA (87); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
@@ -3067,22 +3067,22 @@
       <c r="A110" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B110" s="19" t="inlineStr">
+      <c r="B110" s="20" t="inlineStr">
         <is>
           <t>Pittsburgh, PA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C110" s="19" t="inlineStr">
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>Pittsburgh, PA (97); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D110" s="20" t="inlineStr">
+      <c r="D110" s="17" t="inlineStr">
         <is>
           <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27 — queued for extraction</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
+      <c r="E110" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>
@@ -3093,19 +3093,19 @@
       <c r="A111" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B111" s="19" t="inlineStr">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>St. Paul, MN; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C111" s="19" t="inlineStr">
+      <c r="C111" s="20" t="inlineStr">
         <is>
           <t>St. Paul, MN (68); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
-        <is>
-          <t>Rotterdam; Programme — programme held; abstract book still corrupt — working copy needed from Cat</t>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>Rotterdam; Programme — programme held; the abstract-book file is corrupt — working copy needed from NEV / Cat</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr"/>
@@ -3115,22 +3115,22 @@
       <c r="A112" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B112" s="19" t="inlineStr">
+      <c r="B112" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA; Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="C112" s="19" t="inlineStr">
+      <c r="C112" s="20" t="inlineStr">
         <is>
           <t>New Orleans, LA (61); Schedule — programme ingested (no abstract bodies) — abstract book needed</t>
         </is>
       </c>
-      <c r="D112" s="17" t="inlineStr">
+      <c r="D112" s="18" t="inlineStr">
         <is>
           <t>online; Pending — will be digital</t>
         </is>
       </c>
-      <c r="E112" s="17" t="inlineStr">
+      <c r="E112" s="18" t="inlineStr">
         <is>
           <t>?; Pending — Brit collating (council approval)</t>
         </is>

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -2555,7 +2555,7 @@
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
-          <t>Cardiff; Digital — abstract booklet (Word) from Cat 2026-08-27 — queued for extraction</t>
+          <t>Cardiff; Digital — abstract booklet (Word) found by Ali Hood 2026-08-27; queued for extraction</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr"/>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Galway; Hardcopy — Cat has hardcopy but no scanning capacity — digital needed from IEG (Ireland)</t>
+          <t>Galway; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from IEG (Ireland)</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>Milan; Hardcopy — Cat has hardcopy but no scanning capacity — digital needed from GRIS (Italy)</t>
+          <t>Milan; Hardcopy — Cat holds a hardcopy but has no scanning capacity; digital copy needed from GRIS (Italy)</t>
         </is>
       </c>
       <c r="E98" s="18" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t>Peniche; Programme — 2-page programme only; Cat has hardcopy but no scanning capacity — abstract book needed from APECE (Portugal)</t>
+          <t>Peniche; Programme — 2-page programme only; Cat holds a hardcopy but has no scanning capacity; abstract book needed from APECE (Portugal)</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat has hardcopy but no scanning capacity — abstract book needed from NEV</t>
+          <t>Amsterdam; Schedule — 62 talks ingested, NO abstract bodies; Cat holds a hardcopy but has no scanning capacity; abstract book needed from NEV</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t>Leiden; Programme — programme only — abstract book needed from NEV</t>
+          <t>Leiden; Programme — programme only; abstract book needed from NEV</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>Valencia (=SI2022); Digital — full SI2022 abstract book from Cat 2026-08-27 — queued for extraction</t>
+          <t>Valencia (=SI2022); Digital — full SI2022 abstract book received 2026-08-27; queued for extraction</t>
         </is>
       </c>
       <c r="E108" s="18" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="F108" s="17" t="inlineStr">
         <is>
-          <t>Valencia; Digital — full abstract book received 2026-08-27 — queued (schedule already ingested)</t>
+          <t>Valencia; Digital — full abstract book received 2026-08-27; queued (schedule already ingested)</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D110" s="17" t="inlineStr">
         <is>
-          <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27 — queued for extraction</t>
+          <t>Thessaloniki; Digital — clean abstract book received from Cat 2026-08-27; queued for extraction</t>
         </is>
       </c>
       <c r="E110" s="18" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t>Rotterdam; Programme — programme held; the abstract-book file is corrupt — working copy needed from NEV / Cat</t>
+          <t>Rotterdam; Programme — agenda only; Cat has no abstract book and is unsure one was produced; NEV/Irene to confirm whether it exists</t>
         </is>
       </c>
       <c r="E111" s="13" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>online; Pending — will be digital</t>
+          <t>online; Pending — will be digital (Shark Trust hosting)</t>
         </is>
       </c>
       <c r="E112" s="18" t="inlineStr">

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -56,6 +56,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F0A868"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F6B26B"/>
       </patternFill>
     </fill>
@@ -66,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE599"/>
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD966"/>
+        <fgColor rgb="00FFE599"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,11 +87,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="006AA84F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,10 +142,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,13 +160,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No known source anywhere</t>
+          <t>No known source anywhere.</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -1017,12 +1017,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hardcopy</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Physical book exists (Carylanne / Cat / Ali), not digitised</t>
+          <t>Programme ingested: titles, authors, presentation type. NO abstract text. Useful, but it isn't abstracts.</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
@@ -1030,12 +1030,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Programme</t>
+          <t>Hardcopy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digital PROGRAMME/schedule held, but NOT full abstracts — the abstract book is still needed (see note)</t>
+          <t>A physical book is known to exist (Carylanne, Cat, Ali) but nothing digital. Needs scanning, or a digital copy from the host.</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -1043,12 +1043,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digital ABSTRACT BOOK held &amp; ingestable, not yet ingested</t>
+          <t>A digital programme is held, but not the abstract book. Same practical need as Hardcopy: get the book.</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1056,12 +1056,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Full abstracts ingested but from degraded scans (needs_review) — flatbed re-scan planned</t>
+          <t>A named contact has it or is looking for it, not yet received (EEA: Cat and Ali; OCS: Brit).</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -1069,12 +1069,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Programme ingested: titles/authors/type, NO abstract bodies</t>
+          <t>Abstracts ingested, but from a degraded scan and flagged needs_review. Still worth re-sourcing a clean copy.</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -1082,12 +1082,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ingested</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Full abstracts ingested into the DB</t>
+          <t>Abstract book in hand and ingestable. Only extraction remains.</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -1095,12 +1095,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Ingested</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Available from an external contact, not yet obtained (EEA: Cat; OCS: Brit)</t>
+          <t>Full abstracts ingested into the database.</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>?; Missing — EEA conferences 1-5, no known source</t>
+          <t>?; Missing — 1st EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr"/>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>?; Missing — EEA conferences 1-5, no known source</t>
+          <t>Lisbon; Missing — 2nd EEA; no known abstract source</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>?; Missing — EEA conferences 1-5, no known source</t>
+          <t>?; Missing — 3rd EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>?; Missing — EEA conferences 1-5, no known source</t>
+          <t>?; Missing — 4th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>?; Missing — EEA conferences 1-5, no known source</t>
+          <t>?; Missing — 5th EEA; no known abstract source; host city also unknown</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>San Marino; Pending — 7th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>Monaco; Pending — 9th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>Hamburg; Pending — 10th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>Brest; Pending — 11th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>Lisbon; Pending — 12th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr"/>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Ali Hood searching her paperwork (2026-08-27)</t>
+          <t>Palma de Majorca; Pending — 13th EEA; Ali Hood searching her paperwork (2026-08-27)</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>Adelaide; Pending — joint with ASFB; Brit Finucci confirming</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr"/>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="E102" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
       <c r="F102" s="13" t="inlineStr"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>North Stradbroke Is.; Pending — Moreton Bay Research Station; Brit Finucci confirming</t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
       <c r="F106" s="13" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E108" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
       <c r="F108" s="17" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E110" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>Geelong; Pending — Brit Finucci confirming</t>
         </is>
       </c>
       <c r="F110" s="13" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>?; Pending — Brit collating (council approval)</t>
+          <t>?; Pending — Brit Finucci collating; year/location to confirm</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0A868"/>
+        <fgColor rgb="00ED9C6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,16 +148,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1043,12 +1043,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Programme</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A digital programme is held, but not the abstract book. Same practical need as Hardcopy: get the book.</t>
+          <t>Abstracts ingested, but from a degraded scan and flagged needs_review. Still worth re-sourcing a clean copy.</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1056,12 +1056,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A named contact has it or is looking for it, not yet received (EEA: Cat and Ali; OCS: Brit).</t>
+          <t>A digital programme is held, but not the abstract book. Same practical need as Hardcopy: get the book.</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -1069,12 +1069,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abstracts ingested, but from a degraded scan and flagged needs_review. Still worth re-sourcing a clean copy.</t>
+          <t>A named contact has it or is looking for it, not yet received (EEA: Cat and Ali; OCS: Brit).</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -2855,9 +2855,9 @@
           <t>Reno, NV (128); Ingested</t>
         </is>
       </c>
-      <c r="D101" s="19" t="inlineStr">
-        <is>
-          <t>Peniche; Programme — 2-page programme only; Cat holds a hardcopy but has no scanning capacity; abstract book needed from APECE (Portugal)</t>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>Peniche; Digital — 19th EEA Book of Abstracts (99pp, born-digital) held by Simon all along; queued for extraction</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr"/>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>online (covid); Missing — covid/online — find</t>
+          <t>?; Missing — unknown whether a meeting was held: Cat thinks it was online for covid but was on maternity leave and is unsure; organiser unknown; abstracts unknown</t>
         </is>
       </c>
       <c r="E106" s="18" t="inlineStr">

--- a/outputs/conference_coverage_matrix.xlsx
+++ b/outputs/conference_coverage_matrix.xlsx
@@ -341,6 +341,97 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>% of meetings with abstracts ingested, by society</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$A$43:$A$46</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$D$43:$D$46</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of that society's meetings</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Abstracts over time, by society/series</a:t>
             </a:r>
           </a:p>
@@ -665,12 +756,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3600000"/>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -680,6 +771,28 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -977,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1148,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A physical book is known to exist (Carylanne, Cat, Ali) but nothing digital. Needs scanning, or a digital copy from the host.</t>
+          <t>Physical book known to exist (Carylanne, Cat, Ali) but nothing digital. Needs scanning, or a digital copy.</t>
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -1048,7 +1161,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abstracts ingested, but from a degraded scan and flagged needs_review. Still worth re-sourcing a clean copy.</t>
+          <t>Abstracts ingested, but from a degraded scan and flagged needs_review. Worth re-sourcing a clean copy, ideally digital.</t>
         </is>
       </c>
       <c r="C5" s="5" t="n"/>
@@ -1061,7 +1174,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A digital programme is held, but not the abstract book. Same practical need as Hardcopy: get the book.</t>
+          <t>Digital programme held, not the abstract book. Per Hardcopy: get the book, ideally digital.</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -1074,7 +1187,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A named contact has it or is looking for it, not yet received (EEA: Cat and Ali; OCS: Brit).</t>
+          <t>A named contact has it or is looking for it, not yet received.</t>
         </is>
       </c>
       <c r="C7" s="7" t="n"/>
@@ -1106,80 +1219,70 @@
       <c r="C9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NOTES:</t>
+          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- 'ASIH/JMIH' = the American joint meeting (ASIH pre-1997, JMIH from 1997). ASIH/JMIH/HL/SSAR/NIA share one source book, collapsed to this column to remove duplicates.</t>
+          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- 'AES' (American Elasmobranch Society, founded 1983) kept separate — cell shows elasmo-abstract count where ingested. Pre-1983 = no conference (blank).</t>
+          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Host cities 1916-2025 from github.com/SimonDedman/AESconfLocations; 2026 = New Orleans.</t>
+          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- 'OCR' = degraded 1997-2004 JMIH phone-photo scans (all needs_review); Carylanne's flatbed re-scans would upgrade the non-AES content.</t>
+          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>- AES 1985-2005: full abstracts harvested from elasmo.org/meetings/abstracts/abst&lt;YYYY&gt;/ (1,305 abstracts, 2026-08-25); JMIH-book copies of the same AES talks were removed. No AES source found for 1983-84 or 2006+ online.</t>
+          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>- ASIH/JMIH pre-1992: Carylanne's archive starts 1992 → host city shown but 'Missing'.</t>
+          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>- EEA from Cat Gordon (Shark Trust). 2004-2019 + 2023 ingested via Fable and merged 2026-08-25. Received 2026-08-27: 2002 Cardiff booklet, a clean 2024 Thessaloniki book, and the full SI2022 Valencia abstract book (all queued for extraction). 2025 Rotterdam abstract book is still a corrupt file. Cat holds hardcopies of 2010/2012/2015/2017 but has no scanning capacity, so those are being sought digitally from the host groups; Ali Hood is searching her paperwork for 2003-2009. EEA began in 1997 (2002 Cardiff was the 6th).</t>
+          <t>- Blank/unshaded cell = no conference that year for that series.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
-        <is>
-          <t>- OCS (Oceania Chondrichthyan Soc, ~2011+, biennial): Brit Finucci collating, pending council — years/locations TBC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>- Blank/unshaded cell = no conference that year for that series.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
         <is>
           <t>- Per-society counts &amp; trends: see the Dashboard tab.</t>
         </is>
@@ -3152,7 +3255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4145,6 +4248,92 @@
         <v>1517</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Meetings ingested</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Meetings known</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>% ingested</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AES</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" t="n">
+        <v>44</v>
+      </c>
+      <c r="D43" t="n">
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EEA</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="n">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
